--- a/datasets/cases-100/codex-gpt-5.5/report.xlsx
+++ b/datasets/cases-100/codex-gpt-5.5/report.xlsx
@@ -181,7 +181,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -206,7 +206,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -231,7 +231,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -256,7 +256,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -281,7 +281,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -306,7 +306,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -331,7 +331,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -356,7 +356,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -381,7 +381,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -406,7 +406,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -431,7 +431,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -456,7 +456,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -481,7 +481,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -506,7 +506,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -531,7 +531,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -556,7 +556,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -606,7 +606,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -631,7 +631,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -656,7 +656,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -681,7 +681,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -706,7 +706,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -731,7 +731,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -756,7 +756,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -781,7 +781,7 @@
       <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -806,7 +806,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -831,7 +831,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -856,7 +856,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -881,7 +881,7 @@
       <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -906,7 +906,7 @@
       <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -931,7 +931,7 @@
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -956,7 +956,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -981,7 +981,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1006,7 +1006,7 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1031,7 +1031,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1056,7 +1056,7 @@
       <row>36</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1081,7 +1081,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1106,7 +1106,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1131,7 +1131,7 @@
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1156,7 +1156,7 @@
       <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1181,7 +1181,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1206,7 +1206,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1231,7 +1231,7 @@
       <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1256,7 +1256,7 @@
       <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1281,7 +1281,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1306,7 +1306,7 @@
       <row>46</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1331,7 +1331,7 @@
       <row>47</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1356,7 +1356,7 @@
       <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -1381,7 +1381,7 @@
       <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1406,7 +1406,7 @@
       <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1431,7 +1431,7 @@
       <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1456,7 +1456,7 @@
       <row>52</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -1481,7 +1481,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -1506,7 +1506,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
@@ -1531,7 +1531,7 @@
       <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1556,7 +1556,7 @@
       <row>56</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -1581,7 +1581,7 @@
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1606,7 +1606,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -1631,7 +1631,7 @@
       <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="59" name="Image 59" descr="Picture"/>
@@ -1656,7 +1656,7 @@
       <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="60" name="Image 60" descr="Picture"/>
@@ -1681,7 +1681,7 @@
       <row>61</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="61" name="Image 61" descr="Picture"/>
@@ -1706,7 +1706,7 @@
       <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="62" name="Image 62" descr="Picture"/>
@@ -1731,7 +1731,7 @@
       <row>63</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="63" name="Image 63" descr="Picture"/>
@@ -1756,7 +1756,7 @@
       <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="64" name="Image 64" descr="Picture"/>
@@ -1781,7 +1781,7 @@
       <row>65</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="65" name="Image 65" descr="Picture"/>
@@ -1806,7 +1806,7 @@
       <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="66" name="Image 66" descr="Picture"/>
@@ -1831,7 +1831,7 @@
       <row>67</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="67" name="Image 67" descr="Picture"/>
@@ -1856,7 +1856,7 @@
       <row>68</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="68" name="Image 68" descr="Picture"/>
@@ -1881,7 +1881,7 @@
       <row>69</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="69" name="Image 69" descr="Picture"/>
@@ -1906,7 +1906,7 @@
       <row>70</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
@@ -1931,7 +1931,7 @@
       <row>71</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="71" name="Image 71" descr="Picture"/>
@@ -1956,7 +1956,7 @@
       <row>72</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="72" name="Image 72" descr="Picture"/>
@@ -1981,7 +1981,7 @@
       <row>73</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="73" name="Image 73" descr="Picture"/>
@@ -2006,7 +2006,7 @@
       <row>74</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="74" name="Image 74" descr="Picture"/>
@@ -2031,7 +2031,7 @@
       <row>75</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="75" name="Image 75" descr="Picture"/>
@@ -2056,7 +2056,7 @@
       <row>76</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="76" name="Image 76" descr="Picture"/>
@@ -2081,7 +2081,7 @@
       <row>77</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="77" name="Image 77" descr="Picture"/>
@@ -2106,7 +2106,7 @@
       <row>78</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="78" name="Image 78" descr="Picture"/>
@@ -2131,7 +2131,7 @@
       <row>79</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="79" name="Image 79" descr="Picture"/>
@@ -2156,7 +2156,7 @@
       <row>80</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="80" name="Image 80" descr="Picture"/>
@@ -2181,7 +2181,7 @@
       <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="81" name="Image 81" descr="Picture"/>
@@ -2206,7 +2206,7 @@
       <row>82</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="82" name="Image 82" descr="Picture"/>
@@ -2231,7 +2231,7 @@
       <row>83</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="83" name="Image 83" descr="Picture"/>
@@ -2256,7 +2256,7 @@
       <row>84</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="84" name="Image 84" descr="Picture"/>
@@ -2281,7 +2281,7 @@
       <row>85</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="85" name="Image 85" descr="Picture"/>
@@ -2306,7 +2306,7 @@
       <row>86</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="86" name="Image 86" descr="Picture"/>
@@ -2331,7 +2331,7 @@
       <row>87</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="87" name="Image 87" descr="Picture"/>
@@ -2356,7 +2356,7 @@
       <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="88" name="Image 88" descr="Picture"/>
@@ -2381,7 +2381,7 @@
       <row>89</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="89" name="Image 89" descr="Picture"/>
@@ -2406,7 +2406,7 @@
       <row>90</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="90" name="Image 90" descr="Picture"/>
@@ -2431,7 +2431,7 @@
       <row>91</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="91" name="Image 91" descr="Picture"/>
@@ -2456,7 +2456,7 @@
       <row>92</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="92" name="Image 92" descr="Picture"/>
@@ -2481,7 +2481,7 @@
       <row>93</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="93" name="Image 93" descr="Picture"/>
@@ -2506,7 +2506,7 @@
       <row>94</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="94" name="Image 94" descr="Picture"/>
@@ -2531,7 +2531,7 @@
       <row>95</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="95" name="Image 95" descr="Picture"/>
@@ -2556,7 +2556,7 @@
       <row>96</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="96" name="Image 96" descr="Picture"/>
@@ -2581,7 +2581,7 @@
       <row>97</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="97" name="Image 97" descr="Picture"/>
@@ -2606,7 +2606,7 @@
       <row>98</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="98" name="Image 98" descr="Picture"/>
@@ -2631,7 +2631,7 @@
       <row>99</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="99" name="Image 99" descr="Picture"/>
@@ -2656,7 +2656,7 @@
       <row>100</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="100" name="Image 100" descr="Picture"/>
@@ -2681,7 +2681,7 @@
       <row>101</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1238250" cy="895350"/>
+    <ext cx="1428750" cy="1028700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="101" name="Image 101" descr="Picture"/>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="74.51762940735183" customHeight="1">
+    <row r="2" ht="85.02025506376594" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Case-01-001</t>
@@ -3119,7 +3119,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="74.51762940735183" customHeight="1">
+    <row r="3" ht="85.02025506376594" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Case-01-002</t>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="74.51762940735183" customHeight="1">
+    <row r="4" ht="85.02025506376594" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Case-01-003</t>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="74.51762940735183" customHeight="1">
+    <row r="5" ht="85.02025506376594" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Case-01-004</t>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="74.51762940735183" customHeight="1">
+    <row r="6" ht="85.02025506376594" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Case-01-005</t>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="74.51762940735183" customHeight="1">
+    <row r="7" ht="85.02025506376594" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Case-01-006</t>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="74.51762940735183" customHeight="1">
+    <row r="8" ht="85.02025506376594" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Case-01-007</t>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="74.51762940735183" customHeight="1">
+    <row r="9" ht="85.02025506376594" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Case-01-008</t>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="74.51762940735183" customHeight="1">
+    <row r="10" ht="85.02025506376594" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Case-01-009</t>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="74.51762940735183" customHeight="1">
+    <row r="11" ht="85.02025506376594" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Case-01-010</t>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="74.51762940735183" customHeight="1">
+    <row r="12" ht="85.02025506376594" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Case-01-011</t>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="74.51762940735183" customHeight="1">
+    <row r="13" ht="85.02025506376594" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Case-02-001</t>
@@ -3668,7 +3668,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="74.51762940735183" customHeight="1">
+    <row r="14" ht="85.02025506376594" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Case-02-002</t>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="74.51762940735183" customHeight="1">
+    <row r="15" ht="85.02025506376594" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Case-02-003</t>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="74.51762940735183" customHeight="1">
+    <row r="16" ht="85.02025506376594" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Case-02-004</t>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="74.51762940735183" customHeight="1">
+    <row r="17" ht="85.02025506376594" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Case-02-005</t>
@@ -3872,7 +3872,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="74.51762940735183" customHeight="1">
+    <row r="18" ht="85.02025506376594" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Case-02-006</t>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="74.51762940735183" customHeight="1">
+    <row r="19" ht="85.02025506376594" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Case-02-007</t>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="74.51762940735183" customHeight="1">
+    <row r="20" ht="85.02025506376594" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Case-02-008</t>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="74.51762940735183" customHeight="1">
+    <row r="21" ht="85.02025506376594" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Case-02-009</t>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="74.51762940735183" customHeight="1">
+    <row r="22" ht="85.02025506376594" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Case-03-001</t>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="74.51762940735183" customHeight="1">
+    <row r="23" ht="85.02025506376594" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Case-03-002</t>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="74.51762940735183" customHeight="1">
+    <row r="24" ht="85.02025506376594" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Case-03-003</t>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="74.51762940735183" customHeight="1">
+    <row r="25" ht="85.02025506376594" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Case-03-004</t>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="74.51762940735183" customHeight="1">
+    <row r="26" ht="85.02025506376594" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Case-03-005</t>
@@ -4339,7 +4339,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="74.51762940735183" customHeight="1">
+    <row r="27" ht="85.02025506376594" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Case-03-006</t>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="74.51762940735183" customHeight="1">
+    <row r="28" ht="85.02025506376594" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Case-03-007</t>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="74.51762940735183" customHeight="1">
+    <row r="29" ht="85.02025506376594" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Case-03-008</t>
@@ -4492,7 +4492,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="74.51762940735183" customHeight="1">
+    <row r="30" ht="85.02025506376594" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Case-04-001</t>
@@ -4542,7 +4542,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="74.51762940735183" customHeight="1">
+    <row r="31" ht="85.02025506376594" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Case-04-002</t>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="74.51762940735183" customHeight="1">
+    <row r="32" ht="85.02025506376594" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Case-04-003</t>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="74.51762940735183" customHeight="1">
+    <row r="33" ht="85.02025506376594" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Case-04-005</t>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="74.51762940735183" customHeight="1">
+    <row r="34" ht="85.02025506376594" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Case-04-006</t>
@@ -4748,7 +4748,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="74.51762940735183" customHeight="1">
+    <row r="35" ht="85.02025506376594" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Case-04-007</t>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="74.51762940735183" customHeight="1">
+    <row r="36" ht="85.02025506376594" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Case-04-008</t>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="74.51762940735183" customHeight="1">
+    <row r="37" ht="85.02025506376594" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Case-04-009</t>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="74.51762940735183" customHeight="1">
+    <row r="38" ht="85.02025506376594" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Case-05-001</t>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="74.51762940735183" customHeight="1">
+    <row r="39" ht="85.02025506376594" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Case-05-002</t>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="74.51762940735183" customHeight="1">
+    <row r="40" ht="85.02025506376594" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Case-05-003</t>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="74.51762940735183" customHeight="1">
+    <row r="41" ht="85.02025506376594" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Case-05-004</t>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="74.51762940735183" customHeight="1">
+    <row r="42" ht="85.02025506376594" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Case-05-005</t>
@@ -5159,7 +5159,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="74.51762940735183" customHeight="1">
+    <row r="43" ht="85.02025506376594" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Case-05-006</t>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="74.51762940735183" customHeight="1">
+    <row r="44" ht="85.02025506376594" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Case-05-007</t>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="74.51762940735183" customHeight="1">
+    <row r="45" ht="85.02025506376594" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Case-05-008</t>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="74.51762940735183" customHeight="1">
+    <row r="46" ht="85.02025506376594" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Case-05-009</t>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="74.51762940735183" customHeight="1">
+    <row r="47" ht="85.02025506376594" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Case-06-001</t>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="74.51762940735183" customHeight="1">
+    <row r="48" ht="85.02025506376594" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Case-06-002</t>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="74.51762940735183" customHeight="1">
+    <row r="49" ht="85.02025506376594" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Case-06-003</t>
@@ -5516,7 +5516,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="74.51762940735183" customHeight="1">
+    <row r="50" ht="85.02025506376594" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Case-06-004</t>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="74.51762940735183" customHeight="1">
+    <row r="51" ht="85.02025506376594" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Case-06-005</t>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="74.51762940735183" customHeight="1">
+    <row r="52" ht="85.02025506376594" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Case-06-006</t>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="74.51762940735183" customHeight="1">
+    <row r="53" ht="85.02025506376594" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Case-06-007</t>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="74.51762940735183" customHeight="1">
+    <row r="54" ht="85.02025506376594" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Case-06-008</t>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="74.51762940735183" customHeight="1">
+    <row r="55" ht="85.02025506376594" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Case-06-009</t>
@@ -5821,7 +5821,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="74.51762940735183" customHeight="1">
+    <row r="56" ht="85.02025506376594" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Case-06-010</t>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="74.51762940735183" customHeight="1">
+    <row r="57" ht="85.02025506376594" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Case-07-001</t>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="74.51762940735183" customHeight="1">
+    <row r="58" ht="85.02025506376594" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Case-07-003</t>
@@ -5971,7 +5971,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="74.51762940735183" customHeight="1">
+    <row r="59" ht="85.02025506376594" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Case-07-004</t>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="74.51762940735183" customHeight="1">
+    <row r="60" ht="85.02025506376594" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Case-07-005</t>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="74.51762940735183" customHeight="1">
+    <row r="61" ht="85.02025506376594" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Case-07-006</t>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="74.51762940735183" customHeight="1">
+    <row r="62" ht="85.02025506376594" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Case-07-007</t>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="74.51762940735183" customHeight="1">
+    <row r="63" ht="85.02025506376594" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Case-07-008</t>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="74.51762940735183" customHeight="1">
+    <row r="64" ht="85.02025506376594" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Case-07-009</t>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="74.51762940735183" customHeight="1">
+    <row r="65" ht="85.02025506376594" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Case-08-001</t>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="74.51762940735183" customHeight="1">
+    <row r="66" ht="85.02025506376594" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Case-08-002</t>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="74.51762940735183" customHeight="1">
+    <row r="67" ht="85.02025506376594" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Case-08-003</t>
@@ -6431,7 +6431,7 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="74.51762940735183" customHeight="1">
+    <row r="68" ht="85.02025506376594" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Case-08-004</t>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="74.51762940735183" customHeight="1">
+    <row r="69" ht="85.02025506376594" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Case-08-005</t>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="74.51762940735183" customHeight="1">
+    <row r="70" ht="85.02025506376594" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Case-08-006</t>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="74.51762940735183" customHeight="1">
+    <row r="71" ht="85.02025506376594" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Case-08-007</t>
@@ -6635,7 +6635,7 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="74.51762940735183" customHeight="1">
+    <row r="72" ht="85.02025506376594" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Case-08-008</t>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="74.51762940735183" customHeight="1">
+    <row r="73" ht="85.02025506376594" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Case-08-009</t>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="74.51762940735183" customHeight="1">
+    <row r="74" ht="85.02025506376594" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Case-09-001</t>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="74.51762940735183" customHeight="1">
+    <row r="75" ht="85.02025506376594" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Case-09-002</t>
@@ -6841,7 +6841,7 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="74.51762940735183" customHeight="1">
+    <row r="76" ht="85.02025506376594" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Case-09-003</t>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="74.51762940735183" customHeight="1">
+    <row r="77" ht="85.02025506376594" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Case-09-004</t>
@@ -6943,7 +6943,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="74.51762940735183" customHeight="1">
+    <row r="78" ht="85.02025506376594" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Case-09-005</t>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="74.51762940735183" customHeight="1">
+    <row r="79" ht="85.02025506376594" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Case-09-006</t>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="74.51762940735183" customHeight="1">
+    <row r="80" ht="85.02025506376594" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Case-09-007</t>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="74.51762940735183" customHeight="1">
+    <row r="81" ht="85.02025506376594" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Case-09-008</t>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="74.51762940735183" customHeight="1">
+    <row r="82" ht="85.02025506376594" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Case-10-001</t>
@@ -7200,7 +7200,7 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="74.51762940735183" customHeight="1">
+    <row r="83" ht="85.02025506376594" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Case-10-002</t>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="74.51762940735183" customHeight="1">
+    <row r="84" ht="85.02025506376594" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Case-10-003</t>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="74.51762940735183" customHeight="1">
+    <row r="85" ht="85.02025506376594" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Case-10-004</t>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="74.51762940735183" customHeight="1">
+    <row r="86" ht="85.02025506376594" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Case-10-005</t>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="74.51762940735183" customHeight="1">
+    <row r="87" ht="85.02025506376594" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Case-10-006</t>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
     </row>
-    <row r="88" ht="74.51762940735183" customHeight="1">
+    <row r="88" ht="85.02025506376594" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Case-10-007</t>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="74.51762940735183" customHeight="1">
+    <row r="89" ht="85.02025506376594" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Case-10-008</t>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="74.51762940735183" customHeight="1">
+    <row r="90" ht="85.02025506376594" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Case-11-001</t>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="74.51762940735183" customHeight="1">
+    <row r="91" ht="85.02025506376594" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Case-11-004</t>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="74.51762940735183" customHeight="1">
+    <row r="92" ht="85.02025506376594" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Case-11-005</t>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="74.51762940735183" customHeight="1">
+    <row r="93" ht="85.02025506376594" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Case-11-006</t>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="74.51762940735183" customHeight="1">
+    <row r="94" ht="85.02025506376594" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Case-11-007</t>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="74.51762940735183" customHeight="1">
+    <row r="95" ht="85.02025506376594" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Case-11-008</t>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="74.51762940735183" customHeight="1">
+    <row r="96" ht="85.02025506376594" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Case-11-009</t>
@@ -7915,7 +7915,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="74.51762940735183" customHeight="1">
+    <row r="97" ht="85.02025506376594" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Case-11-010</t>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="74.51762940735183" customHeight="1">
+    <row r="98" ht="85.02025506376594" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Case-11-011</t>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="74.51762940735183" customHeight="1">
+    <row r="99" ht="85.02025506376594" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Case-11-012</t>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="74.51762940735183" customHeight="1">
+    <row r="100" ht="85.02025506376594" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Case-11-013</t>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="74.51762940735183" customHeight="1">
+    <row r="101" ht="85.02025506376594" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Case-11-014</t>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="74.51762940735183" customHeight="1">
+    <row r="102" ht="85.02025506376594" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Case-11-015</t>
